--- a/reports/saudi-systems-issuance.xlsx
+++ b/reports/saudi-systems-issuance.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأنظمة'!$A$1:$M$501</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'المؤرخة'!$A$1:$H$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ملخص'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ملخص'!$A$1:$B$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -785,7 +785,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>موضوعي/تنظيمي</t>
+          <t>قضائي تنظيمي</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>المرافعات والإجراءات</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1094,7 +1094,11 @@
           <t>إجرائي</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>نظام الإجراءات الجزائية</t>
+        </is>
+      </c>
       <c r="H12" s="5" t="n">
         <v>181</v>
       </c>
@@ -1528,15 +1532,19 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>الشركات</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
+          <t>موضوعي/تنظيمي</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>نظام الإفلاس</t>
+        </is>
+      </c>
       <c r="H22" s="5" t="n">
         <v>98</v>
       </c>
@@ -1576,7 +1584,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>موضوعي/تنظيمي</t>
+          <t>إجرائي</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1803,7 +1811,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>موضوعي/تنظيمي</t>
+          <t>قضائي تنظيمي</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
@@ -2354,7 +2362,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>أخرى</t>
+          <t>نظام</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3931,15 +3939,19 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>الجزائي والعقوبات</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr"/>
+          <t>موضوعي/تنظيمي</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>نظام مكافحة المخدرات والمؤثرات العقلية</t>
+        </is>
+      </c>
       <c r="H77" s="5" t="n">
         <v>40</v>
       </c>
@@ -6000,7 +6012,7 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>موضوعي/تنظيمي</t>
+          <t>قضائي تنظيمي</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr"/>
@@ -6043,7 +6055,7 @@
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>موضوعي/تنظيمي</t>
+          <t>قضائي تنظيمي</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr"/>
@@ -7070,15 +7082,19 @@
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>الجزائي والعقوبات</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
-        </is>
-      </c>
-      <c r="G150" s="5" t="inlineStr"/>
+          <t>موضوعي/تنظيمي</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>نظام مكافحة جرائم الإرهاب وتمويله</t>
+        </is>
+      </c>
       <c r="H150" s="5" t="n">
         <v>26</v>
       </c>
@@ -7156,15 +7172,19 @@
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>العقار والتسجيل العيني</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
-        </is>
-      </c>
-      <c r="G152" s="5" t="inlineStr"/>
+          <t>موضوعي/تنظيمي</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>نظام نزع ملكية العقارات للمنفعة العامة ووضع اليد المؤقت على العقار</t>
+        </is>
+      </c>
       <c r="H152" s="5" t="n">
         <v>26</v>
       </c>
@@ -7247,7 +7267,7 @@
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>موضوعي/تنظيمي</t>
+          <t>قضائي تنظيمي</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr"/>
@@ -7973,12 +7993,12 @@
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>غير مصنف</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
+          <t>موضوعي/تنظيمي</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr"/>
@@ -8322,7 +8342,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>موضوعي/تنظيمي</t>
+          <t>إجرائي</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr"/>
@@ -10133,7 +10153,11 @@
           <t>إجرائي</t>
         </is>
       </c>
-      <c r="G221" s="5" t="inlineStr"/>
+      <c r="G221" s="5" t="inlineStr">
+        <is>
+          <t>نظام التحكيم</t>
+        </is>
+      </c>
       <c r="H221" s="5" t="n">
         <v>19</v>
       </c>
@@ -10942,15 +10966,19 @@
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>تنظيمي قطاعي</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr"/>
+          <t>موضوعي/تنظيمي</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="inlineStr">
+        <is>
+          <t>نظام رسوم الأراضي البيضاء</t>
+        </is>
+      </c>
       <c r="H240" s="5" t="n">
         <v>18</v>
       </c>
@@ -11976,7 +12004,7 @@
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>تنظيمي قطاعي</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
@@ -11984,7 +12012,11 @@
           <t>إجرائي</t>
         </is>
       </c>
-      <c r="G264" s="5" t="inlineStr"/>
+      <c r="G264" s="5" t="inlineStr">
+        <is>
+          <t>نظام التكاليف القضائية</t>
+        </is>
+      </c>
       <c r="H264" s="5" t="n">
         <v>17</v>
       </c>
@@ -13223,15 +13255,19 @@
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>تنظيمي قطاعي</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr"/>
+          <t>موضوعي/تنظيمي</t>
+        </is>
+      </c>
+      <c r="G293" s="5" t="inlineStr">
+        <is>
+          <t>نظام الأوسمة السعودية</t>
+        </is>
+      </c>
       <c r="H293" s="5" t="n">
         <v>16</v>
       </c>
@@ -15547,15 +15583,19 @@
       </c>
       <c r="E347" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>غير مصنف</t>
         </is>
       </c>
       <c r="F347" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
-        </is>
-      </c>
-      <c r="G347" s="5" t="inlineStr"/>
+          <t>قضائي تنظيمي</t>
+        </is>
+      </c>
+      <c r="G347" s="5" t="inlineStr">
+        <is>
+          <t>نظام القضاء ونظام ديوان المظالم</t>
+        </is>
+      </c>
       <c r="H347" s="5" t="n">
         <v>15</v>
       </c>
@@ -16058,7 +16098,7 @@
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>أخرى</t>
+          <t>تنظيم</t>
         </is>
       </c>
       <c r="E359" s="5" t="inlineStr">
@@ -18215,15 +18255,19 @@
       </c>
       <c r="E409" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>تنظيمي قطاعي</t>
         </is>
       </c>
       <c r="F409" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
-        </is>
-      </c>
-      <c r="G409" s="5" t="inlineStr"/>
+          <t>موضوعي/تنظيمي</t>
+        </is>
+      </c>
+      <c r="G409" s="5" t="inlineStr">
+        <is>
+          <t>نظام الأحداث</t>
+        </is>
+      </c>
       <c r="H409" s="5" t="n">
         <v>13</v>
       </c>
@@ -18731,15 +18775,19 @@
       </c>
       <c r="E421" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>الإداري والحوكمة العامة</t>
         </is>
       </c>
       <c r="F421" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
-        </is>
-      </c>
-      <c r="G421" s="5" t="inlineStr"/>
+          <t>موضوعي/تنظيمي</t>
+        </is>
+      </c>
+      <c r="G421" s="5" t="inlineStr">
+        <is>
+          <t>نظام المنافسات والمشتريات الحكومية</t>
+        </is>
+      </c>
       <c r="H421" s="5" t="n">
         <v>12</v>
       </c>
@@ -20322,15 +20370,19 @@
       </c>
       <c r="E458" s="5" t="inlineStr">
         <is>
-          <t>التنفيذ</t>
+          <t>الإداري والحوكمة العامة</t>
         </is>
       </c>
       <c r="F458" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
-        </is>
-      </c>
-      <c r="G458" s="5" t="inlineStr"/>
+          <t>موضوعي/تنظيمي</t>
+        </is>
+      </c>
+      <c r="G458" s="5" t="inlineStr">
+        <is>
+          <t>نظام المنافسات والمشتريات الحكومية</t>
+        </is>
+      </c>
       <c r="H458" s="5" t="n">
         <v>8</v>
       </c>
@@ -21571,7 +21623,7 @@
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>القضاء</t>
+          <t>التجاري والشركات</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr">
@@ -21630,7 +21682,7 @@
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>التوثيق والثروة العقارية</t>
+          <t>التوثيق</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
@@ -21689,12 +21741,12 @@
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>القضاء</t>
+          <t>الأحوال الشخصية</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>إجرائي</t>
+          <t>موضوعي/تنظيمي</t>
         </is>
       </c>
       <c r="G489" s="2" t="inlineStr">
@@ -21748,7 +21800,7 @@
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>القضاء</t>
+          <t>المرافعات والإجراءات</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr">
@@ -21807,7 +21859,7 @@
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>القضاء</t>
+          <t>المرافعات والإجراءات</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr">
@@ -21866,7 +21918,7 @@
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>القضاء</t>
+          <t>المرافعات والإجراءات</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr">
@@ -21925,7 +21977,7 @@
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>القضاء</t>
+          <t>المرافعات والإجراءات</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr">
@@ -21984,7 +22036,7 @@
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>القضاء</t>
+          <t>الإثبات</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr">
@@ -22043,7 +22095,7 @@
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>القضاء</t>
+          <t>الإثبات</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr">
@@ -22102,7 +22154,7 @@
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>القضاء</t>
+          <t>الإثبات</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr">
@@ -22159,10 +22211,14 @@
           <t>لائحة</t>
         </is>
       </c>
-      <c r="E497" s="2" t="inlineStr"/>
+      <c r="E497" s="2" t="inlineStr">
+        <is>
+          <t>الأحوال الشخصية</t>
+        </is>
+      </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>إجرائي</t>
+          <t>موضوعي/تنظيمي</t>
         </is>
       </c>
       <c r="G497" s="2" t="inlineStr">
@@ -22216,7 +22272,7 @@
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>المحاماة</t>
+          <t>المرافعات والإجراءات</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
@@ -22275,7 +22331,7 @@
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>القضاء</t>
+          <t>التجاري والشركات</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr">
@@ -22334,12 +22390,12 @@
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>الوثائق الأخرى</t>
+          <t>الشركات</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr">
         <is>
-          <t>إجرائي</t>
+          <t>موضوعي/تنظيمي</t>
         </is>
       </c>
       <c r="G500" s="2" t="inlineStr">
@@ -22391,10 +22447,14 @@
           <t>قواعد</t>
         </is>
       </c>
-      <c r="E501" s="2" t="inlineStr"/>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>الشركات</t>
+        </is>
+      </c>
       <c r="F501" s="2" t="inlineStr">
         <is>
-          <t>إجرائي</t>
+          <t>موضوعي/تنظيمي</t>
         </is>
       </c>
       <c r="G501" s="2" t="inlineStr">
@@ -23022,7 +23082,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>موضوعي/تنظيمي</t>
+          <t>إجرائي</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr"/>
@@ -23198,7 +23258,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
+          <t>موضوعي/تنظيمي</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -23418,7 +23478,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
+          <t>موضوعي/تنظيمي</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -23456,7 +23516,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
+          <t>موضوعي/تنظيمي</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -23566,7 +23626,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>إجرائي</t>
+          <t>موضوعي/تنظيمي</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -23600,7 +23660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -23652,79 +23712,101 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>الأنظمة الإجرائية</t>
+          <t>إجرائي</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>بتاريخ إصدار كامل موثّق — أنظمة أساسية</t>
+          <t>قضائي تنظيمي</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>بتاريخ إصدار كامل موثّق — لوائح وأدوات</t>
+          <t>بتاريخ إصدار كامل موثّق — أنظمة أساسية</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>بسنة إصدار من اسم النظام فقط</t>
+          <t>بتاريخ إصدار كامل موثّق — لوائح وأدوات</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>بلا تاريخ في القاعدة</t>
+          <t>بسنة إصدار من اسم النظام فقط</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>470</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>تاريخ التصدير</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
+          <t>بلا تاريخ في القاعدة</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>470</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>تاريخ التصدير</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>ملاحظة</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>لم يُضَف أي تاريخ غير وارد في مصدر موثّق. تحويل الهجري للميلادي وفق تقويم أم القرى.</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>ملاحظة</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>عمود «الطبيعة» تصنيف آلي بقواعد الاسم؛ واللوائح ترث مجال وطبيعة نظامها الأم.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B11"/>
+  <autoFilter ref="A1:B13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>